--- a/02_readin.xlsx
+++ b/02_readin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oCloud\Home-Cloud\Lehre\BIBB\BIBB_R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCCD696-759F-4F2D-B114-ECCA16E1BAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A81D6A-E490-48A2-8A2B-D4BAC425B008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21540" yWindow="4185" windowWidth="17355" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1824" yWindow="1836" windowWidth="21624" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="02_readin" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Dateityp</t>
   </si>
@@ -56,9 +56,6 @@
     <t>mit `sheet = 1` Tabellenblatt angeben (funktioniert auch mit Namen)</t>
   </si>
   <si>
-    <t xml:space="preserve"> read.table()</t>
-  </si>
-  <si>
     <t>read_dta()</t>
   </si>
   <si>
@@ -90,6 +87,24 @@
   </si>
   <si>
     <t>mit `sep = ";"` Trennzeichen angeben&lt;br&gt;mit row.names= F Zeilennummerierung unterdrücken</t>
+  </si>
+  <si>
+    <t>große .csv</t>
+  </si>
+  <si>
+    <t>{vroom}</t>
+  </si>
+  <si>
+    <t>mit `delim = ";"` Trennzeichen angeben</t>
+  </si>
+  <si>
+    <t>write.table()</t>
+  </si>
+  <si>
+    <t>read.table()</t>
+  </si>
+  <si>
+    <t>vroom()</t>
   </si>
 </sst>
 </file>
@@ -930,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -952,7 +967,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -963,37 +978,51 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1026,13 +1055,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1040,10 +1069,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1051,10 +1080,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,13 +1091,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/02_readin.xlsx
+++ b/02_readin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oCloud\Home-Cloud\Lehre\BIBB\BIBB_R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A81D6A-E490-48A2-8A2B-D4BAC425B008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB04A6D0-5176-4D03-9BC5-3406E8EEB56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1824" yWindow="1836" windowWidth="21624" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="02_readin" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>Dateityp</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>vroom()</t>
+  </si>
+  <si>
+    <t>.Rdata (R format)</t>
+  </si>
+  <si>
+    <t>readRDS</t>
+  </si>
+  <si>
+    <t>saveRDS()</t>
   </si>
 </sst>
 </file>
@@ -945,10 +954,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -962,7 +971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -976,53 +985,64 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1033,10 +1053,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C37D881-CC61-456C-9FB1-EC3BD031E559}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +1070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1064,39 +1084,50 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
     </row>

--- a/02_readin.xlsx
+++ b/02_readin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oCloud\Home-Cloud\Lehre\BIBB\BIBB_R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB04A6D0-5176-4D03-9BC5-3406E8EEB56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E5EA00-08B3-47E2-9667-49F259BB14F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4245" yWindow="4245" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="02_readin" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
   <si>
     <t>Dateityp</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>saveRDS()</t>
+  </si>
+  <si>
+    <t>alle Variableneigenschaften bleiben erhalten</t>
   </si>
 </sst>
 </file>
@@ -955,9 +958,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -985,7 +988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -996,7 +999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1010,7 +1013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1021,7 +1024,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1032,7 +1035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1054,9 +1057,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C37D881-CC61-456C-9FB1-EC3BD031E559}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1070,32 +1073,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1106,7 +1112,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1117,7 +1123,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
